--- a/Main_Release_Daily_Status_Report/PO Details.xlsx
+++ b/Main_Release_Daily_Status_Report/PO Details.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="453" uniqueCount="337">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="334">
   <si>
     <t>Parent ID</t>
   </si>
@@ -244,9 +244,6 @@
     <t>4436246</t>
   </si>
   <si>
-    <t>4436327</t>
-  </si>
-  <si>
     <t>4436379</t>
   </si>
   <si>
@@ -694,9 +691,6 @@
     <t>FY26 [BPMS BAU] - Productivity Updates - Talent Services</t>
   </si>
   <si>
-    <t>Learn from past Solutions (Harvesting Solution Plan)	SG wise prompt updates</t>
-  </si>
-  <si>
     <t>FY26 [BPMS BAU] - Changes related to custom parameter file</t>
   </si>
   <si>
@@ -988,15 +982,15 @@
     <t>sarthak.behera</t>
   </si>
   <si>
+    <t>v.parshotam.thakur</t>
+  </si>
+  <si>
+    <t>a.rajendra.anikhindi and puneet.d.garg</t>
+  </si>
+  <si>
     <t>swati.jaggi</t>
   </si>
   <si>
-    <t>v.parshotam.thakur</t>
-  </si>
-  <si>
-    <t>a.rajendra.anikhindi and puneet.d.garg</t>
-  </si>
-  <si>
     <t>shruti.marathe</t>
   </si>
   <si>
@@ -1016,9 +1010,6 @@
   </si>
   <si>
     <t>rajsingh.j.rajput</t>
-  </si>
-  <si>
-    <t>aditi.b.deshpande and vinny.wadhawan</t>
   </si>
   <si>
     <t>aurv.sharma and prema.ponnurangam</t>
@@ -1356,7 +1347,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C151"/>
+  <dimension ref="A1:C150"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1375,10 +1366,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C2" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1386,10 +1377,10 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C3" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1397,10 +1388,10 @@
         <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C4" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -1408,10 +1399,10 @@
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C5" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -1419,10 +1410,10 @@
         <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C6" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -1430,10 +1421,10 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C7" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -1441,10 +1432,10 @@
         <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C8" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -1452,10 +1443,10 @@
         <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C9" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -1463,10 +1454,10 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C10" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -1474,10 +1465,10 @@
         <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C11" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -1485,10 +1476,10 @@
         <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C12" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -1496,10 +1487,10 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C13" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -1507,10 +1498,10 @@
         <v>15</v>
       </c>
       <c r="B14" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C14" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -1518,10 +1509,10 @@
         <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C15" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -1529,10 +1520,10 @@
         <v>17</v>
       </c>
       <c r="B16" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C16" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -1540,10 +1531,10 @@
         <v>18</v>
       </c>
       <c r="B17" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C17" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -1551,10 +1542,10 @@
         <v>19</v>
       </c>
       <c r="B18" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C18" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -1562,10 +1553,10 @@
         <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C19" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -1573,10 +1564,10 @@
         <v>21</v>
       </c>
       <c r="B20" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C20" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -1584,10 +1575,10 @@
         <v>22</v>
       </c>
       <c r="B21" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C21" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -1595,10 +1586,10 @@
         <v>23</v>
       </c>
       <c r="B22" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C22" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -1606,10 +1597,10 @@
         <v>24</v>
       </c>
       <c r="B23" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C23" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -1617,10 +1608,10 @@
         <v>25</v>
       </c>
       <c r="B24" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C24" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -1628,10 +1619,10 @@
         <v>26</v>
       </c>
       <c r="B25" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C25" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -1639,10 +1630,10 @@
         <v>27</v>
       </c>
       <c r="B26" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C26" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -1650,10 +1641,10 @@
         <v>28</v>
       </c>
       <c r="B27" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C27" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -1661,10 +1652,10 @@
         <v>29</v>
       </c>
       <c r="B28" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C28" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -1672,10 +1663,10 @@
         <v>30</v>
       </c>
       <c r="B29" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C29" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -1683,10 +1674,10 @@
         <v>31</v>
       </c>
       <c r="B30" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C30" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -1694,10 +1685,10 @@
         <v>32</v>
       </c>
       <c r="B31" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C31" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -1705,10 +1696,10 @@
         <v>33</v>
       </c>
       <c r="B32" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C32" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -1716,10 +1707,10 @@
         <v>34</v>
       </c>
       <c r="B33" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C33" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -1727,10 +1718,10 @@
         <v>35</v>
       </c>
       <c r="B34" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C34" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -1738,10 +1729,10 @@
         <v>36</v>
       </c>
       <c r="B35" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C35" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -1749,10 +1740,10 @@
         <v>37</v>
       </c>
       <c r="B36" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C36" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -1760,10 +1751,10 @@
         <v>38</v>
       </c>
       <c r="B37" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C37" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -1771,10 +1762,10 @@
         <v>39</v>
       </c>
       <c r="B38" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C38" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -1782,10 +1773,10 @@
         <v>40</v>
       </c>
       <c r="B39" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C39" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -1793,10 +1784,10 @@
         <v>41</v>
       </c>
       <c r="B40" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C40" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -1804,10 +1795,10 @@
         <v>42</v>
       </c>
       <c r="B41" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C41" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -1815,10 +1806,10 @@
         <v>43</v>
       </c>
       <c r="B42" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C42" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -1826,10 +1817,10 @@
         <v>44</v>
       </c>
       <c r="B43" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C43" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -1837,10 +1828,10 @@
         <v>45</v>
       </c>
       <c r="B44" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C44" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -1848,10 +1839,10 @@
         <v>46</v>
       </c>
       <c r="B45" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C45" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -1859,10 +1850,10 @@
         <v>47</v>
       </c>
       <c r="B46" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C46" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -1870,10 +1861,10 @@
         <v>48</v>
       </c>
       <c r="B47" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C47" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -1881,10 +1872,10 @@
         <v>49</v>
       </c>
       <c r="B48" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C48" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -1892,10 +1883,10 @@
         <v>50</v>
       </c>
       <c r="B49" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C49" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -1903,10 +1894,10 @@
         <v>51</v>
       </c>
       <c r="B50" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C50" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -1914,10 +1905,10 @@
         <v>52</v>
       </c>
       <c r="B51" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C51" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -1925,10 +1916,10 @@
         <v>53</v>
       </c>
       <c r="B52" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C52" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -1936,10 +1927,10 @@
         <v>54</v>
       </c>
       <c r="B53" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C53" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -1947,10 +1938,10 @@
         <v>55</v>
       </c>
       <c r="B54" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C54" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -1958,10 +1949,10 @@
         <v>56</v>
       </c>
       <c r="B55" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C55" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -1969,10 +1960,10 @@
         <v>57</v>
       </c>
       <c r="B56" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C56" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
     </row>
     <row r="57" spans="1:3">
@@ -1980,10 +1971,10 @@
         <v>58</v>
       </c>
       <c r="B57" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C57" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -1991,10 +1982,10 @@
         <v>59</v>
       </c>
       <c r="B58" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C58" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -2002,10 +1993,10 @@
         <v>60</v>
       </c>
       <c r="B59" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C59" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -2013,10 +2004,10 @@
         <v>61</v>
       </c>
       <c r="B60" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C60" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="61" spans="1:3">
@@ -2024,10 +2015,10 @@
         <v>62</v>
       </c>
       <c r="B61" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C61" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -2035,10 +2026,10 @@
         <v>63</v>
       </c>
       <c r="B62" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C62" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -2046,10 +2037,10 @@
         <v>64</v>
       </c>
       <c r="B63" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C63" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -2057,10 +2048,10 @@
         <v>65</v>
       </c>
       <c r="B64" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C64" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
     </row>
     <row r="65" spans="1:3">
@@ -2068,10 +2059,10 @@
         <v>66</v>
       </c>
       <c r="B65" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C65" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
     </row>
     <row r="66" spans="1:3">
@@ -2079,10 +2070,10 @@
         <v>67</v>
       </c>
       <c r="B66" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C66" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
     </row>
     <row r="67" spans="1:3">
@@ -2090,10 +2081,10 @@
         <v>68</v>
       </c>
       <c r="B67" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C67" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="68" spans="1:3">
@@ -2101,10 +2092,10 @@
         <v>69</v>
       </c>
       <c r="B68" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C68" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
     </row>
     <row r="69" spans="1:3">
@@ -2112,10 +2103,10 @@
         <v>70</v>
       </c>
       <c r="B69" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C69" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
     </row>
     <row r="70" spans="1:3">
@@ -2123,10 +2114,10 @@
         <v>71</v>
       </c>
       <c r="B70" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C70" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="71" spans="1:3">
@@ -2134,10 +2125,10 @@
         <v>72</v>
       </c>
       <c r="B71" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C71" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="72" spans="1:3">
@@ -2145,10 +2136,10 @@
         <v>73</v>
       </c>
       <c r="B72" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C72" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="73" spans="1:3">
@@ -2156,10 +2147,10 @@
         <v>74</v>
       </c>
       <c r="B73" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C73" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
     </row>
     <row r="74" spans="1:3">
@@ -2167,10 +2158,10 @@
         <v>75</v>
       </c>
       <c r="B74" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C74" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="75" spans="1:3">
@@ -2178,10 +2169,10 @@
         <v>76</v>
       </c>
       <c r="B75" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C75" t="s">
-        <v>324</v>
+        <v>303</v>
       </c>
     </row>
     <row r="76" spans="1:3">
@@ -2189,10 +2180,10 @@
         <v>77</v>
       </c>
       <c r="B76" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C76" t="s">
-        <v>305</v>
+        <v>322</v>
       </c>
     </row>
     <row r="77" spans="1:3">
@@ -2200,10 +2191,10 @@
         <v>78</v>
       </c>
       <c r="B77" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C77" t="s">
-        <v>325</v>
+        <v>305</v>
       </c>
     </row>
     <row r="78" spans="1:3">
@@ -2211,10 +2202,10 @@
         <v>79</v>
       </c>
       <c r="B78" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C78" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
     </row>
     <row r="79" spans="1:3">
@@ -2222,10 +2213,10 @@
         <v>80</v>
       </c>
       <c r="B79" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C79" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="80" spans="1:3">
@@ -2233,10 +2224,10 @@
         <v>81</v>
       </c>
       <c r="B80" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C80" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="81" spans="1:3">
@@ -2244,10 +2235,10 @@
         <v>82</v>
       </c>
       <c r="B81" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C81" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="82" spans="1:3">
@@ -2255,10 +2246,10 @@
         <v>83</v>
       </c>
       <c r="B82" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C82" t="s">
-        <v>303</v>
+        <v>323</v>
       </c>
     </row>
     <row r="83" spans="1:3">
@@ -2266,10 +2257,10 @@
         <v>84</v>
       </c>
       <c r="B83" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C83" t="s">
-        <v>326</v>
+        <v>301</v>
       </c>
     </row>
     <row r="84" spans="1:3">
@@ -2277,10 +2268,10 @@
         <v>85</v>
       </c>
       <c r="B84" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C84" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="85" spans="1:3">
@@ -2288,10 +2279,10 @@
         <v>86</v>
       </c>
       <c r="B85" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C85" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="86" spans="1:3">
@@ -2299,10 +2290,10 @@
         <v>87</v>
       </c>
       <c r="B86" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C86" t="s">
-        <v>307</v>
+        <v>324</v>
       </c>
     </row>
     <row r="87" spans="1:3">
@@ -2310,10 +2301,10 @@
         <v>88</v>
       </c>
       <c r="B87" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C87" t="s">
-        <v>324</v>
+        <v>304</v>
       </c>
     </row>
     <row r="88" spans="1:3">
@@ -2321,10 +2312,10 @@
         <v>89</v>
       </c>
       <c r="B88" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C88" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="89" spans="1:3">
@@ -2332,10 +2323,10 @@
         <v>90</v>
       </c>
       <c r="B89" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C89" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
     </row>
     <row r="90" spans="1:3">
@@ -2343,10 +2334,10 @@
         <v>91</v>
       </c>
       <c r="B90" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C90" t="s">
-        <v>303</v>
+        <v>316</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -2354,10 +2345,10 @@
         <v>92</v>
       </c>
       <c r="B91" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C91" t="s">
-        <v>318</v>
+        <v>325</v>
       </c>
     </row>
     <row r="92" spans="1:3">
@@ -2365,10 +2356,10 @@
         <v>93</v>
       </c>
       <c r="B92" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C92" t="s">
-        <v>327</v>
+        <v>301</v>
       </c>
     </row>
     <row r="93" spans="1:3">
@@ -2376,10 +2367,10 @@
         <v>94</v>
       </c>
       <c r="B93" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C93" t="s">
-        <v>303</v>
+        <v>316</v>
       </c>
     </row>
     <row r="94" spans="1:3">
@@ -2387,10 +2378,10 @@
         <v>95</v>
       </c>
       <c r="B94" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C94" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
     <row r="95" spans="1:3">
@@ -2398,10 +2389,10 @@
         <v>96</v>
       </c>
       <c r="B95" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C95" t="s">
-        <v>318</v>
+        <v>326</v>
       </c>
     </row>
     <row r="96" spans="1:3">
@@ -2409,10 +2400,10 @@
         <v>97</v>
       </c>
       <c r="B96" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C96" t="s">
-        <v>328</v>
+        <v>316</v>
       </c>
     </row>
     <row r="97" spans="1:3">
@@ -2420,10 +2411,10 @@
         <v>98</v>
       </c>
       <c r="B97" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C97" t="s">
-        <v>318</v>
+        <v>302</v>
       </c>
     </row>
     <row r="98" spans="1:3">
@@ -2431,10 +2422,10 @@
         <v>99</v>
       </c>
       <c r="B98" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C98" t="s">
-        <v>304</v>
+        <v>327</v>
       </c>
     </row>
     <row r="99" spans="1:3">
@@ -2442,10 +2433,10 @@
         <v>100</v>
       </c>
       <c r="B99" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C99" t="s">
-        <v>329</v>
+        <v>317</v>
       </c>
     </row>
     <row r="100" spans="1:3">
@@ -2453,10 +2444,10 @@
         <v>101</v>
       </c>
       <c r="B100" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C100" t="s">
-        <v>319</v>
+        <v>301</v>
       </c>
     </row>
     <row r="101" spans="1:3">
@@ -2464,10 +2455,10 @@
         <v>102</v>
       </c>
       <c r="B101" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C101" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="102" spans="1:3">
@@ -2475,10 +2466,10 @@
         <v>103</v>
       </c>
       <c r="B102" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C102" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="103" spans="1:3">
@@ -2486,10 +2477,10 @@
         <v>104</v>
       </c>
       <c r="B103" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C103" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
     </row>
     <row r="104" spans="1:3">
@@ -2497,10 +2488,10 @@
         <v>105</v>
       </c>
       <c r="B104" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C104" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
     </row>
     <row r="105" spans="1:3">
@@ -2508,10 +2499,10 @@
         <v>106</v>
       </c>
       <c r="B105" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C105" t="s">
-        <v>309</v>
+        <v>328</v>
       </c>
     </row>
     <row r="106" spans="1:3">
@@ -2519,10 +2510,10 @@
         <v>107</v>
       </c>
       <c r="B106" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C106" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
     </row>
     <row r="107" spans="1:3">
@@ -2530,10 +2521,10 @@
         <v>108</v>
       </c>
       <c r="B107" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C107" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="108" spans="1:3">
@@ -2541,10 +2532,10 @@
         <v>109</v>
       </c>
       <c r="B108" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C108" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="109" spans="1:3">
@@ -2552,10 +2543,10 @@
         <v>110</v>
       </c>
       <c r="B109" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C109" t="s">
-        <v>332</v>
+        <v>313</v>
       </c>
     </row>
     <row r="110" spans="1:3">
@@ -2563,10 +2554,10 @@
         <v>111</v>
       </c>
       <c r="B110" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C110" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="111" spans="1:3">
@@ -2574,10 +2565,10 @@
         <v>112</v>
       </c>
       <c r="B111" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C111" t="s">
-        <v>318</v>
+        <v>305</v>
       </c>
     </row>
     <row r="112" spans="1:3">
@@ -2585,10 +2576,10 @@
         <v>113</v>
       </c>
       <c r="B112" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C112" t="s">
-        <v>307</v>
+        <v>331</v>
       </c>
     </row>
     <row r="113" spans="1:3">
@@ -2596,10 +2587,10 @@
         <v>114</v>
       </c>
       <c r="B113" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C113" t="s">
-        <v>333</v>
+        <v>302</v>
       </c>
     </row>
     <row r="114" spans="1:3">
@@ -2607,7 +2598,7 @@
         <v>115</v>
       </c>
       <c r="B114" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C114" t="s">
         <v>304</v>
@@ -2618,10 +2609,10 @@
         <v>116</v>
       </c>
       <c r="B115" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C115" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
     </row>
     <row r="116" spans="1:3">
@@ -2629,10 +2620,10 @@
         <v>117</v>
       </c>
       <c r="B116" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C116" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
     </row>
     <row r="117" spans="1:3">
@@ -2640,10 +2631,10 @@
         <v>118</v>
       </c>
       <c r="B117" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C117" t="s">
-        <v>306</v>
+        <v>318</v>
       </c>
     </row>
     <row r="118" spans="1:3">
@@ -2651,10 +2642,10 @@
         <v>119</v>
       </c>
       <c r="B118" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C118" t="s">
-        <v>334</v>
+        <v>313</v>
       </c>
     </row>
     <row r="119" spans="1:3">
@@ -2662,10 +2653,10 @@
         <v>120</v>
       </c>
       <c r="B119" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C119" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
     </row>
     <row r="120" spans="1:3">
@@ -2673,10 +2664,10 @@
         <v>121</v>
       </c>
       <c r="B120" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C120" t="s">
-        <v>315</v>
+        <v>308</v>
       </c>
     </row>
     <row r="121" spans="1:3">
@@ -2684,7 +2675,7 @@
         <v>122</v>
       </c>
       <c r="B121" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C121" t="s">
         <v>310</v>
@@ -2695,10 +2686,10 @@
         <v>123</v>
       </c>
       <c r="B122" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C122" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
     </row>
     <row r="123" spans="1:3">
@@ -2706,10 +2697,10 @@
         <v>124</v>
       </c>
       <c r="B123" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C123" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
     </row>
     <row r="124" spans="1:3">
@@ -2717,10 +2708,10 @@
         <v>125</v>
       </c>
       <c r="B124" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C124" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
     </row>
     <row r="125" spans="1:3">
@@ -2728,10 +2719,10 @@
         <v>126</v>
       </c>
       <c r="B125" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C125" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
     </row>
     <row r="126" spans="1:3">
@@ -2739,10 +2730,10 @@
         <v>127</v>
       </c>
       <c r="B126" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C126" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
     </row>
     <row r="127" spans="1:3">
@@ -2750,10 +2741,10 @@
         <v>128</v>
       </c>
       <c r="B127" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C127" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
     </row>
     <row r="128" spans="1:3">
@@ -2761,10 +2752,10 @@
         <v>129</v>
       </c>
       <c r="B128" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C128" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="129" spans="1:3">
@@ -2772,10 +2763,10 @@
         <v>130</v>
       </c>
       <c r="B129" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C129" t="s">
-        <v>313</v>
+        <v>305</v>
       </c>
     </row>
     <row r="130" spans="1:3">
@@ -2783,10 +2774,10 @@
         <v>131</v>
       </c>
       <c r="B130" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C130" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
     </row>
     <row r="131" spans="1:3">
@@ -2794,10 +2785,10 @@
         <v>132</v>
       </c>
       <c r="B131" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C131" t="s">
-        <v>321</v>
+        <v>301</v>
       </c>
     </row>
     <row r="132" spans="1:3">
@@ -2805,10 +2796,10 @@
         <v>133</v>
       </c>
       <c r="B132" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C132" t="s">
-        <v>303</v>
+        <v>314</v>
       </c>
     </row>
     <row r="133" spans="1:3">
@@ -2816,10 +2807,10 @@
         <v>134</v>
       </c>
       <c r="B133" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C133" t="s">
-        <v>316</v>
+        <v>308</v>
       </c>
     </row>
     <row r="134" spans="1:3">
@@ -2827,10 +2818,10 @@
         <v>135</v>
       </c>
       <c r="B134" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C134" t="s">
-        <v>310</v>
+        <v>318</v>
       </c>
     </row>
     <row r="135" spans="1:3">
@@ -2838,10 +2829,10 @@
         <v>136</v>
       </c>
       <c r="B135" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C135" t="s">
-        <v>320</v>
+        <v>302</v>
       </c>
     </row>
     <row r="136" spans="1:3">
@@ -2849,10 +2840,10 @@
         <v>137</v>
       </c>
       <c r="B136" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C136" t="s">
-        <v>304</v>
+        <v>316</v>
       </c>
     </row>
     <row r="137" spans="1:3">
@@ -2860,10 +2851,10 @@
         <v>138</v>
       </c>
       <c r="B137" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C137" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
     <row r="138" spans="1:3">
@@ -2871,10 +2862,10 @@
         <v>139</v>
       </c>
       <c r="B138" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C138" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
     <row r="139" spans="1:3">
@@ -2882,10 +2873,10 @@
         <v>140</v>
       </c>
       <c r="B139" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C139" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
     </row>
     <row r="140" spans="1:3">
@@ -2893,10 +2884,10 @@
         <v>141</v>
       </c>
       <c r="B140" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C140" t="s">
-        <v>324</v>
+        <v>309</v>
       </c>
     </row>
     <row r="141" spans="1:3">
@@ -2904,7 +2895,7 @@
         <v>142</v>
       </c>
       <c r="B141" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C141" t="s">
         <v>311</v>
@@ -2915,10 +2906,10 @@
         <v>143</v>
       </c>
       <c r="B142" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C142" t="s">
-        <v>313</v>
+        <v>301</v>
       </c>
     </row>
     <row r="143" spans="1:3">
@@ -2926,10 +2917,10 @@
         <v>144</v>
       </c>
       <c r="B143" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C143" t="s">
-        <v>303</v>
+        <v>313</v>
       </c>
     </row>
     <row r="144" spans="1:3">
@@ -2937,10 +2928,10 @@
         <v>145</v>
       </c>
       <c r="B144" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C144" t="s">
-        <v>315</v>
+        <v>327</v>
       </c>
     </row>
     <row r="145" spans="1:3">
@@ -2948,10 +2939,10 @@
         <v>146</v>
       </c>
       <c r="B145" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C145" t="s">
-        <v>329</v>
+        <v>311</v>
       </c>
     </row>
     <row r="146" spans="1:3">
@@ -2959,10 +2950,10 @@
         <v>147</v>
       </c>
       <c r="B146" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C146" t="s">
-        <v>313</v>
+        <v>332</v>
       </c>
     </row>
     <row r="147" spans="1:3">
@@ -2970,10 +2961,10 @@
         <v>148</v>
       </c>
       <c r="B147" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C147" t="s">
-        <v>335</v>
+        <v>321</v>
       </c>
     </row>
     <row r="148" spans="1:3">
@@ -2981,10 +2972,10 @@
         <v>149</v>
       </c>
       <c r="B148" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C148" t="s">
-        <v>323</v>
+        <v>303</v>
       </c>
     </row>
     <row r="149" spans="1:3">
@@ -2992,10 +2983,10 @@
         <v>150</v>
       </c>
       <c r="B149" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C149" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="150" spans="1:3">
@@ -3003,21 +2994,10 @@
         <v>151</v>
       </c>
       <c r="B150" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C150" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="151" spans="1:3">
-      <c r="A151" t="s">
-        <v>152</v>
-      </c>
-      <c r="B151" t="s">
-        <v>302</v>
-      </c>
-      <c r="C151" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
     </row>
   </sheetData>
